--- a/output/安全衛生規程_いいかいご.xlsx
+++ b/output/安全衛生規程_いいかいご.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -603,456 +603,464 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>第4条　会社は、常時50人未満の事業場であるため法令上の衛生管理者選任義務はないが、必要に応じて衛生推進者を指名し、従業員の健康保持増進活動を推進することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="8" customHeight="1"/>
-    <row r="43" ht="8" customHeight="1">
-      <c r="A43" s="7" t="inlineStr"/>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-    </row>
-    <row r="44" ht="10" customHeight="1"/>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+          <t>第4条　会社は、常時10人以上50人未満の労働者を使用する事業場として、労働安全衛生法に基づき衛生推進者を選任し、その氏名を事業場に掲示して従業員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2　衛生推進者は、健康診断、職場環境の点検、安全衛生教育その他衛生に関する業務を担当する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="8" customHeight="1">
+      <c r="A44" s="7" t="inlineStr"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+    </row>
+    <row r="45" ht="10" customHeight="1"/>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>第3章　健康管理</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>（健康診断）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>第5条　会社は、労働安全衛生法に基づき、従業員に次の健康診断を実施する。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>1　雇入時健康診断（入社時）</t>
+          <t>第5条　会社は、労働安全衛生法に基づき、従業員に次の健康診断を実施する。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2　定期健康診断（年1回。ただし夜勤業務に従事する者については年2回）</t>
+          <t>1　雇入時健康診断（入社時）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>3　特定業務従事者健康診断（必要に応じて）</t>
+          <t>2　定期健康診断（年1回。ただし夜勤業務に従事する者については年2回）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>3　特定業務従事者健康診断（必要に応じて）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>2　健康診断の費用は会社が負担する。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="8" customHeight="1"/>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>（診断結果への対応）</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>第6条　会社は、健康診断の結果に基づき、必要に応じて就業上の措置を講じる。従業員は医師の意見に従い、就業制限や治療を受けなければならない。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="8" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>（ストレスチェック）</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>第7条　会社は、従業員数50人未満のため法定義務はないが、必要に応じてストレスチェックを実施し、結果に基づき職場環境改善や個別対応を行うことができる。</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="8" customHeight="1"/>
-    <row r="59" ht="8" customHeight="1">
-      <c r="A59" s="7" t="inlineStr"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-    </row>
-    <row r="60" ht="10" customHeight="1"/>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="8" customHeight="1">
+      <c r="A60" s="7" t="inlineStr"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+    </row>
+    <row r="61" ht="10" customHeight="1"/>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>第4章　職場環境の整備</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>（作業環境管理）</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>第8条　会社は、職場の換気、採光、照明、温度、騒音等の環境を適正に維持する。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="8" customHeight="1"/>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="65" ht="8" customHeight="1"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>（作業方法の改善）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>第9条　会社は、業務に伴う危険や健康障害を防止するため、作業方法を改善し、安全衛生教育を実施する。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
+          <t>第9条　会社は、業務に伴う危険や健康障害を防止するため、作業方法を改善し、安全衛生教育を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
           <t>2　特に介護業務においては、腰痛予防、福祉用具の適切な使用、送迎業務における車両運転の安全確保に努める。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="8" customHeight="1"/>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="69" ht="8" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>（感染症予防）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>第10条　会社は、インフルエンザ、新型コロナウイルスその他感染症の予防に努め、必要に応じてマスク着用、手指消毒、在宅勤務、出勤停止等の措置を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="8" customHeight="1"/>
-    <row r="72" ht="8" customHeight="1">
-      <c r="A72" s="7" t="inlineStr"/>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="n"/>
-    </row>
-    <row r="73" ht="10" customHeight="1"/>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="8" customHeight="1">
+      <c r="A73" s="7" t="inlineStr"/>
+      <c r="B73" s="8" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
+    </row>
+    <row r="74" ht="10" customHeight="1"/>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>第5章　安全衛生教育</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>（教育の実施）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>第11条　会社は、従業員に対して次の安全衛生教育を実施する。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>1　雇入時教育（安全衛生に関する基本事項）</t>
+          <t>第11条　会社は、従業員に対して次の安全衛生教育を実施する。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2　配置転換時教育（新しい業務に伴う危険防止）</t>
+          <t>1　雇入時教育（安全衛生に関する基本事項）</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>3　作業内容変更時教育（介護・送迎業務における腰痛防止、交通安全等）</t>
+          <t>2　配置転換時教育（新しい業務に伴う危険防止）</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
+          <t>3　作業内容変更時教育（介護・送迎業務における腰痛防止、交通安全等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
           <t>4　定期教育（年1回以上、安全衛生全般に関する教育）</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="8" customHeight="1"/>
-    <row r="82" ht="8" customHeight="1">
-      <c r="A82" s="7" t="inlineStr"/>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="10" customHeight="1"/>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="82" ht="8" customHeight="1"/>
+    <row r="83" ht="8" customHeight="1">
+      <c r="A83" s="7" t="inlineStr"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+    </row>
+    <row r="84" ht="10" customHeight="1"/>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>第6章　労働災害への対応</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>（災害発生時の措置）</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>第12条　労働災害が発生した場合、従業員は直ちに上長に報告し、会社は応急措置を講じ、必要に応じて関係行政官庁へ報告する。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="8" customHeight="1"/>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+    <row r="88" ht="8" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>（再発防止）</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>第13条　会社は、労働災害が発生した場合、その原因を調査し、再発防止策を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="8" customHeight="1"/>
-    <row r="91" ht="8" customHeight="1">
-      <c r="A91" s="7" t="inlineStr"/>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-    </row>
-    <row r="92" ht="10" customHeight="1"/>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="91" ht="8" customHeight="1"/>
+    <row r="92" ht="8" customHeight="1">
+      <c r="A92" s="7" t="inlineStr"/>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="8" t="n"/>
+    </row>
+    <row r="93" ht="10" customHeight="1"/>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>第7章　健康保持・メンタルヘルス</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>（過重労働対策）</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="96" ht="32" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>第14条　会社は、時間外労働や深夜労働が従業員の心身に過度の負担を与えないように管理し、長時間労働が認められる場合は速やかに対応する。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>（メンタルヘルス対応）</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>第15条　会社は、従業員がうつ病、適応障害その他のメンタル不調を抱えた場合、医師の診断や専門家の意見を踏まえ、必要な就業上の措置（休職・勤務軽減・復職支援等）を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="8" customHeight="1"/>
-    <row r="100" ht="8" customHeight="1">
-      <c r="A100" s="7" t="inlineStr"/>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-    </row>
-    <row r="101" ht="10" customHeight="1"/>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="100" ht="8" customHeight="1"/>
+    <row r="101" ht="8" customHeight="1">
+      <c r="A101" s="7" t="inlineStr"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+    </row>
+    <row r="102" ht="10" customHeight="1"/>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>第8章　その他</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>（健康情報の管理）</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>第16条　健康診断やストレスチェックの結果、相談等により得た従業員の個人情報は厳格に管理し、本人の同意なく第三者に開示してはならない。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="8" customHeight="1"/>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+    <row r="106" ht="8" customHeight="1"/>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>（不利益取扱いの禁止）</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>第17条　会社は、従業員が健康診断、感染症予防措置、安全衛生教育等を受けたことを理由に、不利益取扱いをしてはならない。</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="8" customHeight="1"/>
-    <row r="109" ht="8" customHeight="1">
-      <c r="A109" s="7" t="inlineStr"/>
-      <c r="B109" s="8" t="n"/>
-      <c r="C109" s="8" t="n"/>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="8" t="n"/>
-    </row>
-    <row r="110" ht="10" customHeight="1"/>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="8" customHeight="1">
+      <c r="A110" s="7" t="inlineStr"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="10" customHeight="1"/>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、労働基準法、労働安全衛生法その他関係法令による。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
+          <t>1　本規程に定めのない事項は、労働基準法、労働安全衛生法その他関係法令による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
           <t>2　本規程は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A98:E98"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A84:E84"/>
     <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A74:E74"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A101:E101"/>
     <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A42:E42"/>
     <mergeCell ref="A113:E113"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A91:E91"/>
     <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
